--- a/astro-site/public/dl/kit-tareas-asador/07-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-asador/07-semanales-mensuales.xlsx
@@ -11,7 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Semanales" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Mensuales" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tareas Semanales'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tareas Mensuales'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +67,16 @@
       <color rgb="00999999"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -100,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,10 +133,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -484,14 +511,15 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -499,6 +527,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -506,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -534,6 +564,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -541,6 +572,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -569,6 +601,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -576,8 +609,33 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-asador · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -586,7 +644,7 @@
   <sheetPr>
     <tabColor rgb="008B4513"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -614,10 +672,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -642,7 +701,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -659,10 +718,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -688,10 +745,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -717,10 +772,8 @@
       <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -746,10 +799,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -775,10 +826,8 @@
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -804,10 +853,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -832,6 +879,7 @@
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="10" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
@@ -840,10 +888,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -869,10 +915,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -898,10 +942,8 @@
       <c r="G15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -927,10 +969,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -956,10 +996,8 @@
       <c r="G17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="13" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -984,6 +1022,7 @@
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="10" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
@@ -992,10 +1031,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1021,10 +1058,8 @@
       <c r="G21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="13" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1050,10 +1085,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="13" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1079,10 +1112,8 @@
       <c r="G23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1107,6 +1138,27 @@
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="10" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D26">
+        <f>COUNTIF(F5:F24,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F26">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
     <row r="27">
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -1123,13 +1175,32 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1138,7 +1209,7 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1166,10 +1237,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1194,7 +1266,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1211,10 +1283,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1240,10 +1310,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1269,10 +1337,8 @@
       <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1298,10 +1364,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1327,10 +1391,8 @@
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1355,6 +1417,7 @@
       <c r="F10" s="9" t="n"/>
       <c r="G10" s="10" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
@@ -1363,10 +1426,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1392,10 +1453,8 @@
       <c r="G13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1421,10 +1480,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1449,6 +1506,7 @@
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="10" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
@@ -1457,10 +1515,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1486,10 +1542,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1515,10 +1569,8 @@
       <c r="G19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="13" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1544,10 +1596,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1572,6 +1622,27 @@
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="10" t="n"/>
     </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D23">
+        <f>COUNTIF(F5:F21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
     <row r="24">
       <c r="B24" s="12" t="inlineStr">
         <is>
@@ -1588,12 +1659,31 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>